--- a/docs/design-docs/03_画面設計書_点検計画・実施.xlsx
+++ b/docs/design-docs/03_画面設計書_点検計画・実施.xlsx
@@ -15,7 +15,650 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="0" uniqueCount="0"/>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="214">
+  <si>
+    <t>版数</t>
+  </si>
+  <si>
+    <t>改訂日</t>
+  </si>
+  <si>
+    <t>改訂内容</t>
+  </si>
+  <si>
+    <t>改訂者</t>
+  </si>
+  <si>
+    <t>承認者</t>
+  </si>
+  <si>
+    <t>区分</t>
+  </si>
+  <si>
+    <t>備考</t>
+  </si>
+  <si>
+    <t>1.0</t>
+  </si>
+  <si>
+    <t>2026/05/23</t>
+  </si>
+  <si>
+    <t>初版作成</t>
+  </si>
+  <si>
+    <t>システム開発部</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>新規</t>
+  </si>
+  <si>
+    <t>画面設計書 — 年間点検計画一覧</t>
+  </si>
+  <si>
+    <t>文書管理情報</t>
+  </si>
+  <si>
+    <t>システムID</t>
+  </si>
+  <si>
+    <t>STRUTSLAB-001</t>
+  </si>
+  <si>
+    <t>サブシステム名</t>
+  </si>
+  <si>
+    <t>点検計画</t>
+  </si>
+  <si>
+    <t>画面ID</t>
+  </si>
+  <si>
+    <t>SCR-INS-PLAN-001</t>
+  </si>
+  <si>
+    <t>画面名</t>
+  </si>
+  <si>
+    <t>年間点検計画一覧</t>
+  </si>
+  <si>
+    <t>プログラムID</t>
+  </si>
+  <si>
+    <t>PG-INS-PLAN-001</t>
+  </si>
+  <si>
+    <t>文書番号</t>
+  </si>
+  <si>
+    <t>DOC-SCR-SCR-INS-PLAN-001</t>
+  </si>
+  <si>
+    <t>作成日</t>
+  </si>
+  <si>
+    <t>作成者</t>
+  </si>
+  <si>
+    <t>画面レイアウト</t>
+  </si>
+  <si>
+    <t>年度×設備×月マトリクス表示。行=設備、列=4月〜3月(12カラム)。セル内「計画:N回 実績:N回」。未達赤背景、超過黄背景。CSV出力、計画ロック/解除。</t>
+  </si>
+  <si>
+    <t>画面要素一覧</t>
+  </si>
+  <si>
+    <t>要素ID</t>
+  </si>
+  <si>
+    <t>種別</t>
+  </si>
+  <si>
+    <t>表示名</t>
+  </si>
+  <si>
+    <t>入力値/選択肢</t>
+  </si>
+  <si>
+    <t>説明</t>
+  </si>
+  <si>
+    <t>テスト難点タグ</t>
+  </si>
+  <si>
+    <t>plan-year</t>
+  </si>
+  <si>
+    <t>select</t>
+  </si>
+  <si>
+    <t>年度</t>
+  </si>
+  <si>
+    <t>2025/2026/2027</t>
+  </si>
+  <si>
+    <t>plan-cell-{r}-{m}</t>
+  </si>
+  <si>
+    <t>text</t>
+  </si>
+  <si>
+    <t>マトリクスセル</t>
+  </si>
+  <si>
+    <t>計画:N 実績:N</t>
+  </si>
+  <si>
+    <t>動的カラム(12)</t>
+  </si>
+  <si>
+    <t>plan-btn-lock</t>
+  </si>
+  <si>
+    <t>submit</t>
+  </si>
+  <si>
+    <t>計画ロック/解除</t>
+  </si>
+  <si>
+    <t>confirm</t>
+  </si>
+  <si>
+    <t>テーブル列定義</t>
+  </si>
+  <si>
+    <t>列名</t>
+  </si>
+  <si>
+    <t>型</t>
+  </si>
+  <si>
+    <t>ソート</t>
+  </si>
+  <si>
+    <t>設備名</t>
+  </si>
+  <si>
+    <t>VARCHAR</t>
+  </si>
+  <si>
+    <t>4月〜3月</t>
+  </si>
+  <si>
+    <t>動的(12列)</t>
+  </si>
+  <si>
+    <t>Struts1マッピング</t>
+  </si>
+  <si>
+    <t>項目</t>
+  </si>
+  <si>
+    <t>値</t>
+  </si>
+  <si>
+    <t>Action Path</t>
+  </si>
+  <si>
+    <t>/ins/plan/yearly</t>
+  </si>
+  <si>
+    <t>Action Class</t>
+  </si>
+  <si>
+    <t>YearlyPlanAction</t>
+  </si>
+  <si>
+    <t>Form Bean</t>
+  </si>
+  <si>
+    <t>YearlyPlanForm</t>
+  </si>
+  <si>
+    <t>Forward</t>
+  </si>
+  <si>
+    <t>ins.plan.yearly.tiles</t>
+  </si>
+  <si>
+    <t>テスト難点詳細</t>
+  </si>
+  <si>
+    <t>動的カラム(月数=12だが行数可変)</t>
+  </si>
+  <si>
+    <t>色分けCSS class検証</t>
+  </si>
+  <si>
+    <t>ロック後編集不可</t>
+  </si>
+  <si>
+    <t>画面設計書 — 点検計画登録Wizard</t>
+  </si>
+  <si>
+    <t>SCR-INS-PLAN-002</t>
+  </si>
+  <si>
+    <t>点検計画登録Wizard</t>
+  </si>
+  <si>
+    <t>PG-INS-PLAN-002</t>
+  </si>
+  <si>
+    <t>DOC-SCR-SCR-INS-PLAN-002</t>
+  </si>
+  <si>
+    <t>4step Wizard：①対象設備選択→②点検項目テンプレート選択→③日程・担当者→④確認・登録。各step「戻る」「進む」。確認面「一時保存」「確定」。データhidden持回り。</t>
+  </si>
+  <si>
+    <t>wiz-step-indicator</t>
+  </si>
+  <si>
+    <t>step表示</t>
+  </si>
+  <si>
+    <t>①→②→③→④</t>
+  </si>
+  <si>
+    <t>wiz-btn-next-{n}</t>
+  </si>
+  <si>
+    <t>進む</t>
+  </si>
+  <si>
+    <t>hidden値validation</t>
+  </si>
+  <si>
+    <t>wiz-btn-back-{n}</t>
+  </si>
+  <si>
+    <t>戻る</t>
+  </si>
+  <si>
+    <t>前画面data保持</t>
+  </si>
+  <si>
+    <t>wiz-btn-temp-save</t>
+  </si>
+  <si>
+    <t>一時保存</t>
+  </si>
+  <si>
+    <t>session保存</t>
+  </si>
+  <si>
+    <t>wiz-btn-commit</t>
+  </si>
+  <si>
+    <t>確定</t>
+  </si>
+  <si>
+    <t>DB書込</t>
+  </si>
+  <si>
+    <t>/ins/plan/wizard</t>
+  </si>
+  <si>
+    <t>PlanWizardAction</t>
+  </si>
+  <si>
+    <t>PlanWizardForm</t>
+  </si>
+  <si>
+    <t>step1/2/3/confirm</t>
+  </si>
+  <si>
+    <t>4step data持回り(hidden→再POST)</t>
+  </si>
+  <si>
+    <t>戻る→修正→進むloop全path</t>
+  </si>
+  <si>
+    <t>一時保存→session切れ→再開不可</t>
+  </si>
+  <si>
+    <t>画面設計書 — 点検実施一覧(当日)</t>
+  </si>
+  <si>
+    <t>点検実施</t>
+  </si>
+  <si>
+    <t>SCR-INS-DAILY-001</t>
+  </si>
+  <si>
+    <t>点検実施一覧(当日)</t>
+  </si>
+  <si>
+    <t>PG-INS-DAILY-001</t>
+  </si>
+  <si>
+    <t>DOC-SCR-SCR-INS-DAILY-001</t>
+  </si>
+  <si>
+    <t>対象日(本日default)、担当者選択。一覧：設備名、点検種別、予定時刻、status badge(未了=灰/一部完了=黄/完了=緑)、担当者。行click→実施入力直接遷移。</t>
+  </si>
+  <si>
+    <t>daily-date</t>
+  </si>
+  <si>
+    <t>対象日</t>
+  </si>
+  <si>
+    <t>YYYYMMDD</t>
+  </si>
+  <si>
+    <t>daily-status-badge-{n}</t>
+  </si>
+  <si>
+    <t>span</t>
+  </si>
+  <si>
+    <t>status badge</t>
+  </si>
+  <si>
+    <t>未了/一部完了/完了</t>
+  </si>
+  <si>
+    <t>CSS class検証</t>
+  </si>
+  <si>
+    <t>点検種別</t>
+  </si>
+  <si>
+    <t>予定時刻</t>
+  </si>
+  <si>
+    <t>status</t>
+  </si>
+  <si>
+    <t>担当者</t>
+  </si>
+  <si>
+    <t>/ins/daily</t>
+  </si>
+  <si>
+    <t>DailyListAction</t>
+  </si>
+  <si>
+    <t>DailyForm</t>
+  </si>
+  <si>
+    <t>ins.daily.list.tiles</t>
+  </si>
+  <si>
+    <t>badge色分け(CSS class)</t>
+  </si>
+  <si>
+    <t>一覧→実施入力直接遷移param引継</t>
+  </si>
+  <si>
+    <t>画面設計書 — 点検実施入力</t>
+  </si>
+  <si>
+    <t>SCR-INS-EXEC-001</t>
+  </si>
+  <si>
+    <t>点検実施入力</t>
+  </si>
+  <si>
+    <t>PG-INS-EXEC-001</t>
+  </si>
+  <si>
+    <t>DOC-SCR-SCR-INS-EXEC-001</t>
+  </si>
+  <si>
+    <t>3block構成：①設備基本情報(表示) ②checklist 3階層nest table ③総合判定。各項目判定radio(○/×/△)、実測値、所見。×→実測値+所見必須、△→所見必須。写真添付(max5枚/項目)。総合判定異常→異常報告へ。</t>
+  </si>
+  <si>
+    <t>exec-judge-{i}</t>
+  </si>
+  <si>
+    <t>radio</t>
+  </si>
+  <si>
+    <t>判定</t>
+  </si>
+  <si>
+    <t>○/×/△</t>
+  </si>
+  <si>
+    <t>条件付きvalidation</t>
+  </si>
+  <si>
+    <t>全組合わせ=3^N</t>
+  </si>
+  <si>
+    <t>exec-value-{i}</t>
+  </si>
+  <si>
+    <t>実測値</t>
+  </si>
+  <si>
+    <t>×時必須</t>
+  </si>
+  <si>
+    <t>exec-note-{i}</t>
+  </si>
+  <si>
+    <t>textarea</t>
+  </si>
+  <si>
+    <t>所見</t>
+  </si>
+  <si>
+    <t>×/△時必須</t>
+  </si>
+  <si>
+    <t>exec-photo-{i}</t>
+  </si>
+  <si>
+    <t>file</t>
+  </si>
+  <si>
+    <t>写真</t>
+  </si>
+  <si>
+    <t>max5枚/項目</t>
+  </si>
+  <si>
+    <t>file添付</t>
+  </si>
+  <si>
+    <t>exec-summary-judge</t>
+  </si>
+  <si>
+    <t>総合判定</t>
+  </si>
+  <si>
+    <t>正常/異常あり/要観察</t>
+  </si>
+  <si>
+    <t>exec-btn-incident</t>
+  </si>
+  <si>
+    <t>異常報告へ</t>
+  </si>
+  <si>
+    <t>異常時のみ表示</t>
+  </si>
+  <si>
+    <t>条件付button表示</t>
+  </si>
+  <si>
+    <t>data引継</t>
+  </si>
+  <si>
+    <t>/ins/exec/input</t>
+  </si>
+  <si>
+    <t>ExecInputAction</t>
+  </si>
+  <si>
+    <t>ExecForm(ValidatorForm)</t>
+  </si>
+  <si>
+    <t>ins.daily.list / inc.create</t>
+  </si>
+  <si>
+    <t>nest table：tr親子関係DOM上flat</t>
+  </si>
+  <si>
+    <t>条件付きvalidation組合わせ爆発(3^N)</t>
+  </si>
+  <si>
+    <t>写真添付+同時validation</t>
+  </si>
+  <si>
+    <t>異常報告へbutton条件表示</t>
+  </si>
+  <si>
+    <t>画面設計書 — 点検実施詳細・修正</t>
+  </si>
+  <si>
+    <t>SCR-INS-EXEC-002</t>
+  </si>
+  <si>
+    <t>点検実施詳細・修正</t>
+  </si>
+  <si>
+    <t>PG-INS-EXEC-002</t>
+  </si>
+  <si>
+    <t>DOC-SCR-SCR-INS-EXEC-002</t>
+  </si>
+  <si>
+    <t>実施済点検結果全block表示(読取専用)。修正申請→修正理由(textarea必須)→承認申請。承認済は再修正不可。</t>
+  </si>
+  <si>
+    <t>exec-mod-reason</t>
+  </si>
+  <si>
+    <t>修正理由</t>
+  </si>
+  <si>
+    <t>申請時必須</t>
+  </si>
+  <si>
+    <t>exec-mod-status</t>
+  </si>
+  <si>
+    <t>申請status</t>
+  </si>
+  <si>
+    <t>申請中/承認済/差戻</t>
+  </si>
+  <si>
+    <t>/ins/exec/detail</t>
+  </si>
+  <si>
+    <t>ExecDetailAction</t>
+  </si>
+  <si>
+    <t>ExecForm</t>
+  </si>
+  <si>
+    <t>ins.exec.detail.tiles</t>
+  </si>
+  <si>
+    <t>修正申請→承認→再表示全path</t>
+  </si>
+  <si>
+    <t>修正理由validation(申請時のみ必須)</t>
+  </si>
+  <si>
+    <t>承認済後修正不可</t>
+  </si>
+  <si>
+    <t>画面設計書 — 点検実施承認一覧</t>
+  </si>
+  <si>
+    <t>SCR-INS-APPR-001</t>
+  </si>
+  <si>
+    <t>点検実施承認一覧</t>
+  </si>
+  <si>
+    <t>PG-INS-APPR-001</t>
+  </si>
+  <si>
+    <t>DOC-SCR-SCR-INS-APPR-001</t>
+  </si>
+  <si>
+    <t>検索(期間/担当班/status)。一覧checkbox付。一括承認/一括差戻し。差戻時理由必須。操作後通知message。</t>
+  </si>
+  <si>
+    <t>appr-check-{n}</t>
+  </si>
+  <si>
+    <t>checkbox</t>
+  </si>
+  <si>
+    <t>選択</t>
+  </si>
+  <si>
+    <t>appr-btn-approve</t>
+  </si>
+  <si>
+    <t>一括承認</t>
+  </si>
+  <si>
+    <t>appr-btn-reject</t>
+  </si>
+  <si>
+    <t>一括差戻し</t>
+  </si>
+  <si>
+    <t>理由必須</t>
+  </si>
+  <si>
+    <t>confirm+textarea</t>
+  </si>
+  <si>
+    <t>appr-reject-reason</t>
+  </si>
+  <si>
+    <t>差戻理由</t>
+  </si>
+  <si>
+    <t>一括差戻時必須</t>
+  </si>
+  <si>
+    <t>申請日時</t>
+  </si>
+  <si>
+    <t>TIMESTAMP</t>
+  </si>
+  <si>
+    <t>申請者</t>
+  </si>
+  <si>
+    <t>一部表示</t>
+  </si>
+  <si>
+    <t>/ins/approval/list</t>
+  </si>
+  <si>
+    <t>ApprovalListAction</t>
+  </si>
+  <si>
+    <t>ApprovalForm</t>
+  </si>
+  <si>
+    <t>ins.appr.list.tiles</t>
+  </si>
+  <si>
+    <t>一括承認：confirm OK→全件処理</t>
+  </si>
+  <si>
+    <t>一括差戻：confirm→理由必須→未入力validation</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
